--- a/results/exp05-c100-resnet-bw10-40-fedavg-old/20260924-070058/rounds.xlsx
+++ b/results/exp05-c100-resnet-bw10-40-fedavg-old/20260924-070058/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,5650 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:28:52</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.920804346576373</v>
+      </c>
+      <c r="F34" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="G34" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="H34" t="n">
+        <v>29</v>
+      </c>
+      <c r="I34" t="n">
+        <v>49.7779</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0:49.78</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>48.532</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.1158</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1673.675</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>27:53.67</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:29;1:19;3:39;6:20;5:16;9:23;2:13;8:28;4:25;0:35</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[1,4];1:[1];3:[3,4,6];6:[3,4];5:[1];9:[1,3];2:[3];8:[1,3];4:[1,3];0:[1,4,6]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=29,experts=[1,4]; c1:bw=19,experts=[1]; c3:bw=39,experts=[3,4,6]; c6:bw=20,experts=[3,4]; c5:bw=16,experts=[1]; c9:bw=23,experts=[1,3]; c2:bw=13,experts=[3]; c8:bw=28,experts=[1,3]; c4:bw=25,experts=[1,3]; c0:bw=35,experts=[1,4,6]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>4.3601,4.1296,4.9197,6.3128,5.9476,3.3312,3.5585,5.0845,6.4344,4.4536</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:29:42</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.856926700798831</v>
+      </c>
+      <c r="F35" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="G35" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>49.8745</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0:49.87</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>48.6301</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.1108</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1723.5692</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>28:43.57</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:26;1:26;6:27;9:38;8:23;0:12;5:33;7:18;3:40;2:30</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[5,7];1:[3,4];6:[2,4];9:[4,5,6];8:[4,7];0:[3];5:[3,4,6];7:[3];3:[4,5,6,7];2:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=26,experts=[5,7]; c1:bw=26,experts=[3,4]; c6:bw=27,experts=[2,4]; c9:bw=38,experts=[4,5,6]; c8:bw=23,experts=[4,7]; c0:bw=12,experts=[3]; c5:bw=33,experts=[3,4,6]; c7:bw=18,experts=[3]; c3:bw=40,experts=[4,5,6,7]; c2:bw=30,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>6.4717,4.1388,6.3507,3.3587,5.0878,4.4743,5.9507,4.3590,4.8780,3.5605</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:30:32</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.854513948815927</v>
+      </c>
+      <c r="F36" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="G36" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="H36" t="n">
+        <v>35</v>
+      </c>
+      <c r="I36" t="n">
+        <v>49.7849</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0:49.78</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>48.5449</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.1091</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1773.3738</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>29:33.37</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:18;0:11;1:17;6:24;2:25;8:28;9:15;7:27;5:23;3:13</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[4];0:[5];1:[2];6:[4,7];2:[4,7];8:[4,5];9:[7];7:[4,7];5:[4,7];3:[4]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=18,experts=[4]; c0:bw=11,experts=[5]; c1:bw=17,experts=[2]; c6:bw=24,experts=[4,7]; c2:bw=25,experts=[4,7]; c8:bw=28,experts=[4,5]; c9:bw=15,experts=[7]; c7:bw=27,experts=[4,7]; c5:bw=23,experts=[4,7]; c3:bw=13,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>6.4885,4.4882,4.1152,6.2957,3.5578,5.0560,3.3721,4.3874,5.9296,4.8543</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:31:22</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.824972837469643</v>
+      </c>
+      <c r="F37" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="G37" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>49.8846</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0:49.88</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>48.632</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.1168</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1823.4823</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>30:23.48</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:21;0:20;3:33;7:15;6:24;5:27;1:10;4:40;8:28;2:28</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[4,6];0:[2,7];3:[0,4,6];7:[4];6:[0,4];5:[2,4];1:[5];4:[0,2,4,6];8:[4,6];2:[2,4]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=21,experts=[4,6]; c0:bw=20,experts=[2,7]; c3:bw=33,experts=[0,4,6]; c7:bw=15,experts=[4]; c6:bw=24,experts=[0,4]; c5:bw=27,experts=[2,4]; c1:bw=10,experts=[5]; c4:bw=40,experts=[0,2,4,6]; c8:bw=28,experts=[4,6]; c2:bw=28,experts=[2,4]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>3.3528,4.4914,4.9045,4.3685,6.2998,5.9142,4.1403,6.4616,5.1224,3.5764</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:32:12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.79193012069153</v>
+      </c>
+      <c r="F38" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="G38" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>49.9681</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0:49.97</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>48.7019</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.1393</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1873.4706</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>31:13.47</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:10;5:22;2:20;6:36;4:22;7:23;9:22;0:30;3:20;8:10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[7];5:[4,6];2:[4,6];6:[0,4,6];4:[4,6];7:[4,6];9:[2,4];0:[0,4,6];3:[2,4];8:[4]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[7]; c5:bw=22,experts=[4,6]; c2:bw=20,experts=[4,6]; c6:bw=36,experts=[0,4,6]; c4:bw=22,experts=[4,6]; c7:bw=23,experts=[4,6]; c9:bw=22,experts=[2,4]; c0:bw=30,experts=[0,4,6]; c3:bw=20,experts=[2,4]; c8:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>4.1685,6.0013,3.6030,6.3676,6.4635,4.3668,3.3559,4.4715,4.8316,5.0723</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:33:04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.840529988224923</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37</v>
+      </c>
+      <c r="I39" t="n">
+        <v>52.7701</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0:52.77</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>51.4204</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.2076</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1926.2615</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>32:06.26</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:25;6:10;4:29;1:17;5:10;2:10;3:21;7:28;9:14;0:22</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[5];4:[4,6];1:[6];5:[5];2:[0];3:[4,6];7:[2,4];9:[0];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=25,experts=[4,6]; c6:bw=10,experts=[5]; c4:bw=29,experts=[4,6]; c1:bw=17,experts=[6]; c5:bw=10,experts=[5]; c2:bw=10,experts=[0]; c3:bw=21,experts=[4,6]; c7:bw=28,experts=[2,4]; c9:bw=14,experts=[0]; c0:bw=22,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>5.5463,6.8718,6.9362,4.1530,5.9043,3.5462,5.1655,4.7604,3.6605,4.8763</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:33:55</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.753622598265419</v>
+      </c>
+      <c r="F40" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="G40" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="H40" t="n">
+        <v>39</v>
+      </c>
+      <c r="I40" t="n">
+        <v>50.1678</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0:50.17</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>48.9159</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.1222</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1976.4555</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>32:56.46</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:14;0:10;1:25;7:22;6:17;8:25;2:20;4:20;9:13;5:40</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[4];0:[4];1:[0,4];7:[4,5];6:[4];8:[2,4];2:[4,6];4:[4,6];9:[4];5:[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=14,experts=[4]; c0:bw=10,experts=[4]; c1:bw=25,experts=[0,4]; c7:bw=22,experts=[4,5]; c6:bw=17,experts=[4]; c8:bw=25,experts=[2,4]; c2:bw=20,experts=[4,6]; c4:bw=20,experts=[4,6]; c9:bw=13,experts=[4]; c5:bw=40,experts=[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5.1986,4.5353,4.1441,4.3475,6.2960,5.0900,3.5807,6.4388,3.3365,5.9484</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:34:45</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.761974473322733</v>
+      </c>
+      <c r="F41" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="G41" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="H41" t="n">
+        <v>39</v>
+      </c>
+      <c r="I41" t="n">
+        <v>49.8762</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0:49.88</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>48.6042</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.1371</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2026.3529</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>33:46.35</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:14;1:23;5:18;6:26;2:36;7:37;3:10;4:11;9:22;0:20</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[0];1:[4,6];5:[4];6:[1,4];2:[1,4,6];7:[0,4,6];3:[1];4:[4];9:[4,6];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=14,experts=[0]; c1:bw=23,experts=[4,6]; c5:bw=18,experts=[4]; c6:bw=26,experts=[1,4]; c2:bw=36,experts=[1,4,6]; c7:bw=37,experts=[0,4,6]; c3:bw=10,experts=[1]; c4:bw=11,experts=[4]; c9:bw=22,experts=[4,6]; c0:bw=20,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>5.1469,4.1572,5.9621,6.3340,3.5883,4.3499,4.8512,6.3778,3.3262,4.5107</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:35:34</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.761143792850795</v>
+      </c>
+      <c r="F42" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="H42" t="n">
+        <v>39</v>
+      </c>
+      <c r="I42" t="n">
+        <v>49.7456</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0:49.75</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>48.4628</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.1476</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2076.1203</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>34:36.12</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:30;6:10;8:31;1:10;4:28;5:34;7:38;3:22;9:30;0:10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[3,4,6];6:[3];8:[1,3,4];1:[1];4:[1,3];5:[1,4,6];7:[1,4,6];3:[3,4];9:[1,3,4];0:[1]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[3,4,6]; c6:bw=10,experts=[3]; c8:bw=31,experts=[1,3,4]; c1:bw=10,experts=[1]; c4:bw=28,experts=[1,3]; c5:bw=34,experts=[1,4,6]; c7:bw=38,experts=[1,4,6]; c3:bw=22,experts=[3,4]; c9:bw=30,experts=[1,3,4]; c0:bw=10,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3.5839,6.3153,5.0619,4.1281,6.3835,5.9859,4.3652,4.8432,3.3415,4.4542</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:36:24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.770198404763644</v>
+      </c>
+      <c r="F43" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="G43" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="H43" t="n">
+        <v>39</v>
+      </c>
+      <c r="I43" t="n">
+        <v>49.8527</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0:49.85</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>48.6063</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.1103</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2125.9949</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>35:25.99</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:28;1:27;3:27;9:28;6:19;0:10;7:11;4:30;8:23;2:22</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[3,4];1:[3,4];3:[5,7];9:[4,5];6:[2];0:[3];7:[3];4:[4,5,7];8:[4,7];2:[4,5]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=28,experts=[3,4]; c1:bw=27,experts=[3,4]; c3:bw=27,experts=[5,7]; c9:bw=28,experts=[4,5]; c6:bw=19,experts=[2]; c0:bw=10,experts=[3]; c7:bw=11,experts=[3]; c4:bw=30,experts=[4,5,7]; c8:bw=23,experts=[4,7]; c2:bw=22,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>5.9363,4.1810,4.8767,3.3724,6.3062,4.4538,4.3619,6.4529,5.1202,3.5447</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:37:14</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.784998081550547</v>
+      </c>
+      <c r="F44" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="G44" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="H44" t="n">
+        <v>39</v>
+      </c>
+      <c r="I44" t="n">
+        <v>49.8482</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0:49.85</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>48.5345</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.1816</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2175.8668</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>36:15.87</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:29;1:32;2:28;8:25;9:18;7:12;4:19;6:10;3:36;0:12</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[4,7];1:[2,4,6];2:[4,7];8:[4,5];9:[7];7:[7];4:[4];6:[7];3:[0,4,6];0:[5]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[4,7]; c1:bw=32,experts=[2,4,6]; c2:bw=28,experts=[4,7]; c8:bw=25,experts=[4,5]; c9:bw=18,experts=[7]; c7:bw=12,experts=[7]; c4:bw=19,experts=[4]; c6:bw=10,experts=[7]; c3:bw=36,experts=[0,4,6]; c0:bw=12,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>5.9288,4.1477,3.5461,5.0831,3.3811,4.3603,6.3986,6.3445,4.8765,4.4677</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:38:04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.699267919505318</v>
+      </c>
+      <c r="F45" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="G45" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>49.8043</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0:49.80</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>48.5492</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.1212</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2225.6929</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>37:05.69</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:37;3:26;4:16;2:20;7:40;5:13;6:11;9:21;8:19;1:25</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[2,4,7];3:[4,6];4:[0];2:[2,4];7:[0,1,4,6];5:[2];6:[4];9:[4,6];8:[4];1:[4,5]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=37,experts=[2,4,7]; c3:bw=26,experts=[4,6]; c4:bw=16,experts=[0]; c2:bw=20,experts=[2,4]; c7:bw=40,experts=[0,1,4,6]; c5:bw=13,experts=[2]; c6:bw=11,experts=[4]; c9:bw=21,experts=[4,6]; c8:bw=19,experts=[4]; c1:bw=25,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4.5141,4.8684,6.3912,3.5651,4.3783,5.9874,6.3017,3.3443,5.0735,4.1252</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:38:54</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.708277211419961</v>
+      </c>
+      <c r="F46" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="G46" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>50.0493</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0:50.05</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>48.7822</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2275.9704</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>37:55.97</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:31;0:20;3:37;4:36;7:20;2:27;9:14;6:10;5:25;1:31</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[0,4,6];0:[0,4];3:[2,4,6];4:[2,4,6];7:[4,6];2:[4,6];9:[2];6:[0];5:[4,6];1:[4,6,7]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=31,experts=[0,4,6]; c0:bw=20,experts=[0,4]; c3:bw=37,experts=[2,4,6]; c4:bw=36,experts=[2,4,6]; c7:bw=20,experts=[4,6]; c2:bw=27,experts=[4,6]; c9:bw=14,experts=[2]; c6:bw=10,experts=[0]; c5:bw=25,experts=[4,6]; c1:bw=31,experts=[4,6,7]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5.1542,4.5399,4.8813,6.4587,4.3830,3.5591,3.3502,6.3373,5.9726,4.1459</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:39:44</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.710870445585127</v>
+      </c>
+      <c r="F47" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="G47" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>49.9837</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0:49.98</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>48.7285</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1334</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.1205</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2325.9758</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>38:45.98</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:20;3:15;6:21;1:23;4:35;5:23;2:32;8:22;0:30;7:16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[0,4];3:[4];6:[5,6];1:[4,6];4:[0,4,6];5:[4,6];2:[0,4,6];8:[4,6];0:[0,4,6];7:[2]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=20,experts=[0,4]; c3:bw=15,experts=[4]; c6:bw=21,experts=[5,6]; c1:bw=23,experts=[4,6]; c4:bw=35,experts=[0,4,6]; c5:bw=23,experts=[4,6]; c2:bw=32,experts=[0,4,6]; c8:bw=22,experts=[4,6]; c0:bw=30,experts=[0,4,6]; c7:bw=16,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>3.3777,4.9015,6.4078,4.1312,6.4760,5.9335,3.5709,5.0814,4.4933,4.3551</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:40:37</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.674224050167183</v>
+      </c>
+      <c r="F48" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="G48" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47</v>
+      </c>
+      <c r="I48" t="n">
+        <v>53.0505</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0:53.05</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>51.7892</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.1271</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2379.0491</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>39:39.05</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:29;6:12;7:29;9:10;8:22;3:39;4:10;0:25;1:17;2:30</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[0,5];6:[4];7:[4,5];9:[4];8:[2,4];3:[0,4,6];4:[4];0:[4,6];1:[0];2:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[0,5]; c6:bw=12,experts=[4]; c7:bw=29,experts=[4,5]; c9:bw=10,experts=[4]; c8:bw=22,experts=[2,4]; c3:bw=39,experts=[0,4,6]; c4:bw=10,experts=[4]; c0:bw=25,experts=[4,6]; c1:bw=17,experts=[0]; c2:bw=30,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>6.1656,6.8990,4.7736,3.8098,5.7761,5.3296,6.7213,4.5501,4.1705,3.5934</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:41:28</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.661981925531968</v>
+      </c>
+      <c r="F49" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="G49" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" t="n">
+        <v>50.5583</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0:50.56</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>49.3115</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.1153</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2429.6314</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>40:29.63</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:28;8:28;4:37;2:31;9:29;6:25;5:31;7:35;0:10;3:10</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[4,6];8:[4,6];4:[0,4,6];2:[1,4,6];9:[4,6];6:[1,4];5:[0,4,6];7:[0,4,6];0:[4];3:[1]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[4,6]; c8:bw=28,experts=[4,6]; c4:bw=37,experts=[0,4,6]; c2:bw=31,experts=[1,4,6]; c9:bw=29,experts=[4,6]; c6:bw=25,experts=[1,4]; c5:bw=31,experts=[0,4,6]; c7:bw=35,experts=[0,4,6]; c0:bw=10,experts=[4]; c3:bw=10,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>4.1736,5.3105,6.7923,3.7342,3.3734,6.2705,5.9425,4.3808,4.5023,4.8314</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:42:18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.712778393650624</v>
+      </c>
+      <c r="F50" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="G50" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H50" t="n">
+        <v>48</v>
+      </c>
+      <c r="I50" t="n">
+        <v>49.977</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0:49.98</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>48.7299</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.1104</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2479.6331</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>41:19.63</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:27;3:18;8:15;0:11;2:32;5:31;6:10;7:24;9:29;1:30</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[1,3];3:[3];8:[1];0:[1];2:[3,4,6];5:[1,4,6];6:[3];7:[4,6];9:[1,3];1:[1,4,6]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=27,experts=[1,3]; c3:bw=18,experts=[3]; c8:bw=15,experts=[1]; c0:bw=11,experts=[1]; c2:bw=32,experts=[3,4,6]; c5:bw=31,experts=[1,4,6]; c6:bw=10,experts=[3]; c7:bw=24,experts=[4,6]; c9:bw=29,experts=[1,3]; c1:bw=30,experts=[1,4,6]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>6.4874,4.8858,5.1102,4.4945,3.5879,5.9323,6.3281,4.3890,3.3708,4.1439</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:43:08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.73028719136999</v>
+      </c>
+      <c r="F51" t="n">
+        <v>51</v>
+      </c>
+      <c r="G51" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H51" t="n">
+        <v>48</v>
+      </c>
+      <c r="I51" t="n">
+        <v>49.806</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0:49.81</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>48.5465</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.1291</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2529.4624</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>42:09.46</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:18;4:10;7:19;6:38;2:35;1:36;3:22;0:16;9:15;5:17</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[3];4:[5];7:[3];6:[2,4,6];2:[4,5,6];1:[3,4,6];3:[5,7];0:[3];9:[5];5:[3]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=18,experts=[3]; c4:bw=10,experts=[5]; c7:bw=19,experts=[3]; c6:bw=38,experts=[2,4,6]; c2:bw=35,experts=[4,5,6]; c1:bw=36,experts=[3,4,6]; c3:bw=22,experts=[5,7]; c0:bw=16,experts=[3]; c9:bw=15,experts=[5]; c5:bw=17,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>5.1135,6.4112,4.3199,6.3201,3.5745,4.1441,4.8444,4.4672,3.3678,5.9837</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:43:58</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.733479790192198</v>
+      </c>
+      <c r="F52" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="G52" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H52" t="n">
+        <v>48</v>
+      </c>
+      <c r="I52" t="n">
+        <v>50.0696</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0:50.07</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>48.8182</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.1186</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2579.556</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>42:59.56</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:26;0:30;1:12;2:11;8:26;6:29;9:10;3:31;4:10;7:15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[4,7];0:[4,5,6];1:[2];2:[7];8:[5,7];6:[4,7];9:[7];3:[0,4,6];4:[7];7:[7]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=26,experts=[4,7]; c0:bw=30,experts=[4,5,6]; c1:bw=12,experts=[2]; c2:bw=11,experts=[7]; c8:bw=26,experts=[5,7]; c6:bw=29,experts=[4,7]; c9:bw=10,experts=[7]; c3:bw=31,experts=[0,4,6]; c4:bw=10,experts=[7]; c7:bw=15,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>5.9689,4.5448,4.1782,3.5517,5.1393,6.4500,3.3848,4.8533,6.4240,4.3232</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:44:48</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.6896996708937</v>
+      </c>
+      <c r="F53" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="G53" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H53" t="n">
+        <v>48</v>
+      </c>
+      <c r="I53" t="n">
+        <v>49.8419</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0:49.84</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>48.5891</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.1251</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2629.4218</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>43:49.42</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:26;8:10;5:13;7:19;1:22;4:18;9:17;6:28;2:16;3:24</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[2,7];8:[4];5:[2];7:[1];1:[4,5];4:[4];9:[4];6:[4,6];2:[2];3:[4,6]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[2,7]; c8:bw=10,experts=[4]; c5:bw=13,experts=[2]; c7:bw=19,experts=[1]; c1:bw=22,experts=[4,5]; c4:bw=18,experts=[4]; c9:bw=17,experts=[4]; c6:bw=28,experts=[4,6]; c2:bw=16,experts=[2]; c3:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4.5420,5.0772,5.9953,4.3229,4.1333,6.4350,3.3821,6.3209,3.5206,4.8599</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:45:38</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.636287478902328</v>
+      </c>
+      <c r="F54" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="G54" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H54" t="n">
+        <v>48</v>
+      </c>
+      <c r="I54" t="n">
+        <v>50.0425</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0:50.04</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>48.7833</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.1233</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2679.4887</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>44:39.49</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:12;4:16;5:24;1:33;3:26;9:34;6:20;7:24;0:21;2:29</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[0];4:[2];5:[4,6];1:[4,6,7];3:[2,4];9:[2,4,6];6:[0,4];7:[4,6];0:[4,6];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[0]; c4:bw=16,experts=[2]; c5:bw=24,experts=[4,6]; c1:bw=33,experts=[4,6,7]; c3:bw=26,experts=[2,4]; c9:bw=34,experts=[2,4,6]; c6:bw=20,experts=[0,4]; c7:bw=24,experts=[4,6]; c0:bw=21,experts=[4,6]; c2:bw=29,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>5.1202,6.4886,5.9680,4.1723,4.8672,3.3721,6.3205,4.3745,4.5211,3.5787</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:46:28</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.608605471372024</v>
+      </c>
+      <c r="F55" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="G55" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="H55" t="n">
+        <v>54</v>
+      </c>
+      <c r="I55" t="n">
+        <v>50.0341</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0:50.03</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>48.7754</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.1262</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2729.5472</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>45:29.55</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:29;8:31;7:34;3:17;0:20;6:30;5:10;9:28;4:18</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[4];1:[4,6];8:[0,4,6];7:[2,4,6];3:[4];0:[0,4];6:[4,5,6];5:[4];9:[0,4];4:[4]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[4]; c1:bw=29,experts=[4,6]; c8:bw=31,experts=[0,4,6]; c7:bw=34,experts=[2,4,6]; c3:bw=17,experts=[4]; c0:bw=20,experts=[0,4]; c6:bw=30,experts=[4,5,6]; c5:bw=10,experts=[4]; c9:bw=28,experts=[0,4]; c4:bw=18,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>3.5933,4.1951,5.1458,4.3969,4.8508,4.5552,6.3255,5.9009,3.3814,6.4304</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:47:18</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.60482349274491</v>
+      </c>
+      <c r="F56" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="G56" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55</v>
+      </c>
+      <c r="I56" t="n">
+        <v>49.8323</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0:49.83</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>48.5824</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.1187</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2779.4045</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>46:19.40</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:30;2:23;4:10;3:29;8:10;5:29;1:33;6:23;0:15;9:34</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[4,5,6];2:[0,4];4:[4];3:[4,6];8:[2];5:[4,5];1:[0,4,6];6:[4,6];0:[4];9:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=30,experts=[4,5,6]; c2:bw=23,experts=[0,4]; c4:bw=10,experts=[4]; c3:bw=29,experts=[4,6]; c8:bw=10,experts=[2]; c5:bw=29,experts=[4,5]; c1:bw=33,experts=[0,4,6]; c6:bw=23,experts=[4,6]; c0:bw=15,experts=[4]; c9:bw=34,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>4.4117,3.5701,6.4325,4.8684,5.0931,5.9077,4.1440,6.3142,4.4713,3.3694</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:48:08</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.629919883686283</v>
+      </c>
+      <c r="F57" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="G57" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="H57" t="n">
+        <v>55</v>
+      </c>
+      <c r="I57" t="n">
+        <v>50.8698</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0:50.87</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>49.622</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.1114</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2830.2998</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>47:10.30</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:29;1:31;3:10;2:29;5:17;4:10;8:10;7:10;6:13;0:39</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[4,6];1:[0,4,6];3:[1];2:[1,4];5:[0];4:[0];8:[4];7:[0];6:[1];0:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[4,6]; c1:bw=31,experts=[0,4,6]; c3:bw=10,experts=[1]; c2:bw=29,experts=[1,4]; c5:bw=17,experts=[0]; c4:bw=10,experts=[0]; c8:bw=10,experts=[4]; c7:bw=10,experts=[0]; c6:bw=13,experts=[1]; c0:bw=39,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>3.3763,4.1693,4.8580,3.5743,5.9674,6.4350,5.2318,4.6558,6.7230,4.6309</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:48:58</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.607126222152514</v>
+      </c>
+      <c r="F58" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="G58" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="H58" t="n">
+        <v>57</v>
+      </c>
+      <c r="I58" t="n">
+        <v>49.9034</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0:49.90</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>48.6441</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.1292</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2880.2285</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>48:00.23</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:35;8:24;6:27;1:27;7:38;0:39;5:24;4:23;2:18;9:11</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[3,4,6];8:[1,4];6:[3,4];1:[1,4];7:[0,4,6];0:[1,4,6];5:[1,4];4:[1,6];2:[3];9:[1]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=35,experts=[3,4,6]; c8:bw=24,experts=[1,4]; c6:bw=27,experts=[3,4]; c1:bw=27,experts=[1,4]; c7:bw=38,experts=[0,4,6]; c0:bw=39,experts=[1,4,6]; c5:bw=24,experts=[1,4]; c4:bw=23,experts=[1,6]; c2:bw=18,experts=[3]; c9:bw=11,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>4.9245,5.0978,6.3087,4.1173,4.3631,4.5182,5.9203,6.4430,3.5641,3.3871</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:49:48</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.626417824676486</v>
+      </c>
+      <c r="F59" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="H59" t="n">
+        <v>57</v>
+      </c>
+      <c r="I59" t="n">
+        <v>50.0471</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0:50.05</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>48.7911</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.1194</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2930.3007</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>48:50.30</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:13;2:10;9:32;6:30;5:19;1:17;8:22;4:21;3:34;0:26</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[3];2:[5];9:[3,4,5];6:[2,4,6];5:[3];1:[3];8:[3,4];4:[3,5];3:[4,5,7];0:[3,4]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=13,experts=[3]; c2:bw=10,experts=[5]; c9:bw=32,experts=[3,4,5]; c6:bw=30,experts=[2,4,6]; c5:bw=19,experts=[3]; c1:bw=17,experts=[3]; c8:bw=22,experts=[3,4]; c4:bw=21,experts=[3,5]; c3:bw=34,experts=[4,5,7]; c0:bw=26,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>4.3629,3.5893,3.3817,6.3402,6.0173,4.1337,5.0908,6.4957,4.8643,4.5153</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:50:39</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.625065273964661</v>
+      </c>
+      <c r="F60" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="G60" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="H60" t="n">
+        <v>57</v>
+      </c>
+      <c r="I60" t="n">
+        <v>50.1559</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0:50.16</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>48.8933</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.1344</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2980.4825</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>49:40.48</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:20;8:31;9:15;6:11;1:36;4:14;7:15;5:18;0:29;3:20</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[4,7];8:[4,5,7];9:[7];6:[7];1:[2,4,6];4:[7];7:[7];5:[7];0:[4,5];3:[0,4]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=20,experts=[4,7]; c8:bw=31,experts=[4,5,7]; c9:bw=15,experts=[7]; c6:bw=11,experts=[7]; c1:bw=36,experts=[2,4,6]; c4:bw=14,experts=[7]; c7:bw=15,experts=[7]; c5:bw=18,experts=[7]; c0:bw=29,experts=[4,5]; c3:bw=20,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>3.6155,5.1588,3.3700,6.3784,4.1495,6.4772,4.3411,6.0116,4.5270,4.8642</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:51:29</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.586340072946975</v>
+      </c>
+      <c r="F61" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="G61" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="H61" t="n">
+        <v>57</v>
+      </c>
+      <c r="I61" t="n">
+        <v>50.1562</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0:50.16</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>48.9028</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.1192</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3030.6642</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>50:30.66</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:29;7:26;4:17;2:17;5:18;8:14;6:33;9:10;1:30;3:24</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[2,7];7:[1,4];4:[4];2:[2];5:[2];8:[4];6:[0,4,6];9:[4];1:[4,5,6];3:[4,6]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=29,experts=[2,7]; c7:bw=26,experts=[1,4]; c4:bw=17,experts=[4]; c2:bw=17,experts=[2]; c5:bw=18,experts=[2]; c8:bw=14,experts=[4]; c6:bw=33,experts=[0,4,6]; c9:bw=10,experts=[4]; c1:bw=30,experts=[4,5,6]; c3:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>4.5476,4.4144,6.4918,3.5936,6.0149,5.1308,6.3455,3.3647,4.1486,4.8508</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:52:19</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.579465753185095</v>
+      </c>
+      <c r="F62" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="G62" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="H62" t="n">
+        <v>61</v>
+      </c>
+      <c r="I62" t="n">
+        <v>50.0976</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0:50.10</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>48.8281</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.1317</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3080.7896</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>51:20.79</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:27;6:21;2:16;9:21;1:19;3:24;8:31;4:21;7:24;0:33</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[4,6];6:[4,6];2:[6];9:[2,4];1:[7];3:[2,4];8:[0,4,6];4:[2,4];7:[4,6];0:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=27,experts=[4,6]; c6:bw=21,experts=[4,6]; c2:bw=16,experts=[6]; c9:bw=21,experts=[2,4]; c1:bw=19,experts=[7]; c3:bw=24,experts=[2,4]; c8:bw=31,experts=[0,4,6]; c4:bw=21,experts=[2,4]; c7:bw=24,experts=[4,6]; c0:bw=33,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>5.9990,6.3968,3.5894,3.3682,4.1505,4.8434,5.1104,6.4632,4.3824,4.5248</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:53:09</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.548040541207664</v>
+      </c>
+      <c r="F63" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="G63" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="H63" t="n">
+        <v>62</v>
+      </c>
+      <c r="I63" t="n">
+        <v>50.2891</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0:50.29</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>49.0172</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.1393</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3131.1049</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>52:11.10</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:10;6:35;9:10;4:33;5:37;0:16;3:29;2:23;1:40;7:25</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[4];6:[4,5,6];9:[4];4:[0,4,6];5:[0,4,6];0:[4];3:[4,6];2:[4,6];1:[0,1,4,6];7:[2,4]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[4]; c6:bw=35,experts=[4,5,6]; c9:bw=10,experts=[4]; c4:bw=33,experts=[0,4,6]; c5:bw=37,experts=[0,4,6]; c0:bw=16,experts=[4]; c3:bw=29,experts=[4,6]; c2:bw=23,experts=[4,6]; c1:bw=40,experts=[0,1,4,6]; c7:bw=25,experts=[2,4]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>5.1455,6.3891,3.3963,6.5288,5.9810,4.5105,4.9014,3.6157,4.1511,4.3979</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:53:59</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.578902038836122</v>
+      </c>
+      <c r="F64" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="G64" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="H64" t="n">
+        <v>62</v>
+      </c>
+      <c r="I64" t="n">
+        <v>50.1679</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0:50.17</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>48.9202</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3181.3006</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>53:01.30</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:12;6:19;3:29;8:18;1:28;7:38;0:23;2:15;4:29</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[5];9:[0];6:[4];3:[4,6];8:[2];1:[4,6];7:[4,5,6];0:[4,6];2:[0];4:[4,6]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[5]; c9:bw=12,experts=[0]; c6:bw=19,experts=[4]; c3:bw=29,experts=[4,6]; c8:bw=18,experts=[2]; c1:bw=28,experts=[4,6]; c7:bw=38,experts=[4,5,6]; c0:bw=23,experts=[4,6]; c2:bw=15,experts=[0]; c4:bw=29,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>6.0582,3.4130,6.3416,4.8654,5.0682,4.1383,4.4004,4.5580,3.5656,6.5115</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:54:50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.53316147086451</v>
+      </c>
+      <c r="F65" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="G65" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="H65" t="n">
+        <v>64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>50.2734</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0:50.27</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>48.9878</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.1549</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3231.6016</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>53:51.60</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:28;4:21;5:13;3:21;7:19;0:18;8:30;9:33;2:31;1:16</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[1,4];4:[4,6];5:[4];3:[1,4];7:[4];0:[4];8:[0,4,6];9:[0,4,6];2:[1,4,6];1:[4]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=28,experts=[1,4]; c4:bw=21,experts=[4,6]; c5:bw=13,experts=[4]; c3:bw=21,experts=[1,4]; c7:bw=19,experts=[4]; c0:bw=18,experts=[4]; c8:bw=30,experts=[0,4,6]; c9:bw=33,experts=[0,4,6]; c2:bw=31,experts=[1,4,6]; c1:bw=16,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>6.3758,6.5495,5.9751,4.8532,4.3892,4.5427,5.1301,3.3755,3.6628,4.1339</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:55:40</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.562420211900569</v>
+      </c>
+      <c r="F66" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="G66" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="H66" t="n">
+        <v>64</v>
+      </c>
+      <c r="I66" t="n">
+        <v>50.6311</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0:50.63</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>49.2893</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.1992</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3282.2595</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>54:42.26</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:16;4:32;6:28;8:37;3:24;0:23;2:16;1:32;9:26</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[0];5:[1];4:[1,4,6];6:[3,4];8:[1,4,6];3:[3,4];0:[1,4];2:[3];1:[0,4,6];9:[1,4]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[0]; c5:bw=16,experts=[1]; c4:bw=32,experts=[1,4,6]; c6:bw=28,experts=[3,4]; c8:bw=37,experts=[1,4,6]; c3:bw=24,experts=[3,4]; c0:bw=23,experts=[1,4]; c2:bw=16,experts=[3]; c1:bw=32,experts=[0,4,6]; c9:bw=26,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>4.3741,6.0514,6.5371,6.3367,5.1201,4.8627,4.5427,3.5519,4.3041,3.6085</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:56:31</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.558452298452957</v>
+      </c>
+      <c r="F67" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="G67" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="H67" t="n">
+        <v>64</v>
+      </c>
+      <c r="I67" t="n">
+        <v>50.7561</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0:50.76</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>49.5064</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.1195</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3333.0492</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>55:33.05</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:23;5:10;1:30;8:13;9:17;6:16;4:23;0:21;3:37;7:28</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[4,5];5:[3];1:[3,4,6];8:[3];9:[3];6:[2];4:[3,5];0:[3,4];3:[4,5,7];7:[3,4]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=23,experts=[4,5]; c5:bw=10,experts=[3]; c1:bw=30,experts=[3,4,6]; c8:bw=13,experts=[3]; c9:bw=17,experts=[3]; c6:bw=16,experts=[2]; c4:bw=23,experts=[3,5]; c0:bw=21,experts=[3,4]; c3:bw=37,experts=[4,5,7]; c7:bw=28,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>3.9075,6.3012,4.1738,5.1019,3.3838,6.3623,6.5002,4.5317,4.8530,4.3910</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:57:22</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.535781750639418</v>
+      </c>
+      <c r="F68" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="G68" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="H68" t="n">
+        <v>64</v>
+      </c>
+      <c r="I68" t="n">
+        <v>50.2417</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0:50.24</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>48.9876</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.1214</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3383.3187</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>56:23.32</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:28;5:27;1:20;3:14;6:29;0:18;2:24;9:33;7:33;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[4,7];5:[4,7];1:[2,4];3:[0];6:[4,7];0:[5];2:[4,7];9:[4,5,7];7:[4,6,7];8:[5]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=28,experts=[4,7]; c5:bw=27,experts=[4,7]; c1:bw=20,experts=[2,4]; c3:bw=14,experts=[0]; c6:bw=29,experts=[4,7]; c0:bw=18,experts=[5]; c2:bw=24,experts=[4,7]; c9:bw=33,experts=[4,5,7]; c7:bw=33,experts=[4,6,7]; c8:bw=10,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>6.5567,6.0534,4.1791,4.8785,6.3212,4.5162,3.5812,3.3753,4.4375,5.0884</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:58:12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.546923776596877</v>
+      </c>
+      <c r="F69" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="G69" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="H69" t="n">
+        <v>64</v>
+      </c>
+      <c r="I69" t="n">
+        <v>50.2601</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0:50.26</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>48.9827</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.1432</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3433.607</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>57:13.61</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:23;8:17;2:32;0:17;3:14;4:27;5:25;9:10;7:15;6:18</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[4,5];8:[7];2:[2,4,6];0:[2];3:[4];4:[4,6];5:[2,4];9:[4];7:[1];6:[0]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=23,experts=[4,5]; c8:bw=17,experts=[7]; c2:bw=32,experts=[2,4,6]; c0:bw=17,experts=[2]; c3:bw=14,experts=[4]; c4:bw=27,experts=[4,6]; c5:bw=25,experts=[2,4]; c9:bw=10,experts=[4]; c7:bw=15,experts=[1]; c6:bw=18,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>4.1826,5.1017,3.6043,4.5211,4.8933,6.4911,6.0071,3.3862,4.3731,6.4221</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:59:02</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.520304949235281</v>
+      </c>
+      <c r="F70" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="G70" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H70" t="n">
+        <v>69</v>
+      </c>
+      <c r="I70" t="n">
+        <v>50.2214</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0:50.22</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>48.9435</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.1473</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3483.8565</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>58:03.86</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:23;7:32;1:17;4:23;9:20;5:22;0:29;2:37;8:23;6:15</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[2,4];7:[0,4,6];1:[7];4:[2,4];9:[2,4];5:[4,6];0:[0,7];2:[0,4,6];8:[4,6];6:[4]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=23,experts=[2,4]; c7:bw=32,experts=[0,4,6]; c1:bw=17,experts=[7]; c4:bw=23,experts=[2,4]; c9:bw=20,experts=[2,4]; c5:bw=22,experts=[4,6]; c0:bw=29,experts=[0,7]; c2:bw=37,experts=[0,4,6]; c8:bw=23,experts=[4,6]; c6:bw=15,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>4.9238,4.4151,4.1687,6.4557,3.3767,5.9841,4.5539,3.5892,5.1328,6.3434</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:59:52</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.524421844676233</v>
+      </c>
+      <c r="F71" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="G71" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H71" t="n">
+        <v>69</v>
+      </c>
+      <c r="I71" t="n">
+        <v>50.2125</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0:50.21</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>48.9631</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.1162</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3534.0976</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>58:54.10</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:13;9:10;7:16;3:18;0:17;6:14;2:31;4:32;5:13;8:27</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[1];9:[4];7:[2];3:[4];0:[4];6:[5];2:[1,4,6];4:[0,4,6];5:[0];8:[4,6]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=13,experts=[1]; c9:bw=10,experts=[4]; c7:bw=16,experts=[2]; c3:bw=18,experts=[4]; c0:bw=17,experts=[4]; c6:bw=14,experts=[5]; c2:bw=31,experts=[1,4,6]; c4:bw=32,experts=[0,4,6]; c5:bw=13,experts=[0]; c8:bw=27,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>4.1914,3.3963,4.3920,4.8820,4.5438,6.3443,3.5755,6.4797,6.0505,5.1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:00:43</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.521985598538986</v>
+      </c>
+      <c r="F72" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="G72" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H72" t="n">
+        <v>69</v>
+      </c>
+      <c r="I72" t="n">
+        <v>50.2231</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0:50.22</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>48.952</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.1373</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3584.3501</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>59:44.35</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:24;0:10;1:29;9:22;7:11;5:19;3:34;6:28;8:21;2:34</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[4,6];0:[6];1:[4,6];9:[4,6];7:[5];5:[5];3:[0,4,6];6:[4,6];8:[2,4];2:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=24,experts=[4,6]; c0:bw=10,experts=[6]; c1:bw=29,experts=[4,6]; c9:bw=22,experts=[4,6]; c7:bw=11,experts=[5]; c5:bw=19,experts=[5]; c3:bw=34,experts=[0,4,6]; c6:bw=28,experts=[4,6]; c8:bw=21,experts=[2,4]; c2:bw=34,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>6.5423,4.5692,4.1908,3.3987,4.3494,6.0062,4.9022,6.3394,5.0788,3.5750</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:01:33</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.498372976859702</v>
+      </c>
+      <c r="F73" t="n">
+        <v>60.97</v>
+      </c>
+      <c r="G73" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H73" t="n">
+        <v>69</v>
+      </c>
+      <c r="I73" t="n">
+        <v>50.4038</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0:50.40</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>49.1162</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.1353</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3634.783</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:00:34.78</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:16;1:22;5:24;7:27;6:11;0:29;3:13;2:13;9:21;4:22</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[0];1:[4,6];5:[4,6];7:[4,6];6:[1];0:[4,6];3:[1];2:[4];9:[0,4];4:[4,6]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=16,experts=[0]; c1:bw=22,experts=[4,6]; c5:bw=24,experts=[4,6]; c7:bw=27,experts=[4,6]; c6:bw=11,experts=[1]; c0:bw=29,experts=[4,6]; c3:bw=13,experts=[1]; c2:bw=13,experts=[4]; c9:bw=21,experts=[0,4]; c4:bw=22,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>5.1611,4.2060,6.0315,4.4066,6.3913,4.5928,4.8710,3.5623,3.3898,6.5038</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:02:23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.503741560587495</v>
+      </c>
+      <c r="F74" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="G74" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H74" t="n">
+        <v>69</v>
+      </c>
+      <c r="I74" t="n">
+        <v>50.2196</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0:50.22</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>48.929</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.1558</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3685.0323</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:01:25.03</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:26;8:10;3:22;1:37;5:10;9:29;0:16;7:20;6:11;4:23</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[3,4];8:[1];3:[3,4];1:[0,4,6];5:[1];9:[1,4];0:[1];7:[4,6];6:[3];4:[1,4]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=26,experts=[3,4]; c8:bw=10,experts=[1]; c3:bw=22,experts=[3,4]; c1:bw=37,experts=[0,4,6]; c5:bw=10,experts=[1]; c9:bw=29,experts=[1,4]; c0:bw=16,experts=[1]; c7:bw=20,experts=[4,6]; c6:bw=11,experts=[3]; c4:bw=23,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>3.5940,5.0945,4.9193,4.1951,6.0145,3.3699,4.5100,4.3957,6.3594,6.4766</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:03:14</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.517260433811842</v>
+      </c>
+      <c r="F75" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H75" t="n">
+        <v>69</v>
+      </c>
+      <c r="I75" t="n">
+        <v>50.3607</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0:50.36</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>49.0975</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1353</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3735.4228</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:02:15.42</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:22;1:15;5:28;7:36;8:16;6:10;2:10;4:26;9:18</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[5];0:[3,4];1:[3];5:[3,4];7:[3,4,6];8:[3];6:[2];2:[5];4:[3,5];9:[3]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[5]; c0:bw=22,experts=[3,4]; c1:bw=15,experts=[3]; c5:bw=28,experts=[3,4]; c7:bw=36,experts=[3,4,6]; c8:bw=16,experts=[3]; c6:bw=10,experts=[2]; c2:bw=10,experts=[5]; c4:bw=26,experts=[3,5]; c9:bw=18,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>4.9357,4.5956,4.1790,6.0090,4.3967,5.0954,6.4159,3.5634,6.5140,3.3929</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:04:05</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.488125304723048</v>
+      </c>
+      <c r="F76" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="G76" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="H76" t="n">
+        <v>75</v>
+      </c>
+      <c r="I76" t="n">
+        <v>51.6298</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0:51.63</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>50.3696</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.1234</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3787.0828</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:03:07.08</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:22;9:34;1:30;3:11;7:16;6:31;5:17;4:31;0:34;8:30</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[4,7];9:[4,5,7];1:[2,4,6];3:[7];7:[7];6:[4,6,7];5:[7];4:[4,6,7];0:[4,5,6];8:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=22,experts=[4,7]; c9:bw=34,experts=[4,5,7]; c1:bw=30,experts=[2,4,6]; c3:bw=11,experts=[7]; c7:bw=16,experts=[7]; c6:bw=31,experts=[4,6,7]; c5:bw=17,experts=[7]; c4:bw=31,experts=[4,6,7]; c0:bw=34,experts=[4,5,6]; c8:bw=30,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>3.6052,3.6143,4.5135,5.2386,4.6614,6.4100,6.0556,6.5580,4.5810,5.1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:04:56</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.493449175769334</v>
+      </c>
+      <c r="F77" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="G77" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="H77" t="n">
+        <v>75</v>
+      </c>
+      <c r="I77" t="n">
+        <v>51.0394</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0:51.04</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>49.7788</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.1315</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3838.1523</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:03:58.15</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:16;5:21;0:17;3:10;2:14;6:13;7:37;4:34;9:32;1:30</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[7];5:[2,4];0:[2];3:[4];2:[2];6:[0];7:[1,4,6];4:[0,4,6];9:[0,4,6];1:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=16,experts=[7]; c5:bw=21,experts=[2,4]; c0:bw=17,experts=[2]; c3:bw=10,experts=[4]; c2:bw=14,experts=[2]; c6:bw=13,experts=[0]; c7:bw=37,experts=[1,4,6]; c4:bw=34,experts=[0,4,6]; c9:bw=32,experts=[0,4,6]; c1:bw=30,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>5.0996,6.1492,4.6324,4.9581,3.8098,6.6668,4.4046,6.5151,3.3814,4.1617</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:05:47</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.48020727440224</v>
+      </c>
+      <c r="F78" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="G78" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="H78" t="n">
+        <v>77</v>
+      </c>
+      <c r="I78" t="n">
+        <v>50.611</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0:50.61</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>49.3588</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.1196</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3888.7962</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:04:48.80</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:16;2:19;1:35;8:10;4:10;7:10;6:32;0:35;3:22;5:33</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[2];2:[4];1:[4,6,7];8:[4];4:[2];7:[0];6:[0,4,6];0:[0,4,7];3:[2,4];5:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=16,experts=[2]; c2:bw=19,experts=[4]; c1:bw=35,experts=[4,6,7]; c8:bw=10,experts=[4]; c4:bw=10,experts=[2]; c7:bw=10,experts=[0]; c6:bw=32,experts=[0,4,6]; c0:bw=35,experts=[0,4,7]; c3:bw=22,experts=[2,4]; c5:bw=33,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>3.5385,3.6172,4.2119,5.1440,6.6198,4.3407,6.3530,4.5752,4.9173,6.0412</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:06:38</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.464166597495506</v>
+      </c>
+      <c r="F79" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="G79" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="H79" t="n">
+        <v>78</v>
+      </c>
+      <c r="I79" t="n">
+        <v>50.9008</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0:50.90</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>49.5897</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.1704</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3939.7275</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:05:39.73</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:15;4:13;3:21;7:20;8:30;1:23;9:17;6:32;5:35;2:19</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[4];4:[4];3:[4,6];7:[2,4];8:[0,4,6];1:[1,4];9:[4];6:[4,5,6];5:[0,4,6];2:[1]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=15,experts=[4]; c4:bw=13,experts=[4]; c3:bw=21,experts=[4,6]; c7:bw=20,experts=[2,4]; c8:bw=30,experts=[0,4,6]; c1:bw=23,experts=[1,4]; c9:bw=17,experts=[4]; c6:bw=32,experts=[4,5,6]; c5:bw=35,experts=[0,4,6]; c2:bw=19,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>4.5959,6.5313,4.8971,4.4100,5.1168,4.1847,3.3849,6.5276,6.2594,3.6820</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:07:36</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.463110900232809</v>
+      </c>
+      <c r="F80" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="G80" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="H80" t="n">
+        <v>79</v>
+      </c>
+      <c r="I80" t="n">
+        <v>57.9016</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0:57.90</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>56.2736</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.4724</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3997.6624</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:06:37.66</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:12;9:10;0:20;4:40;7:25;8:25;5:29;3:15;1:21;2:18</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[4];9:[4];0:[4,6];4:[0,2,4,6];7:[4,5];8:[2,4];5:[4,5];3:[0];1:[4,6];2:[0]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=12,experts=[4]; c9:bw=10,experts=[4]; c0:bw=20,experts=[4,6]; c4:bw=40,experts=[0,2,4,6]; c7:bw=25,experts=[4,5]; c8:bw=25,experts=[2,4]; c5:bw=29,experts=[4,5]; c3:bw=15,experts=[0]; c1:bw=21,experts=[4,6]; c2:bw=18,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>6.5863,3.4205,4.6345,6.6013,4.4861,6.2385,7.9630,6.2696,5.3780,4.6959</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:08:40</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.453946638858977</v>
+      </c>
+      <c r="F81" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
+      <c r="I81" t="n">
+        <v>63.9091</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:03.91</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>62.3839</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.3695</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4061.6139</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:07:41.61</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:36;9:29;7:26;1:17;3:17;4:32;2:24;0:26;6:22;8:28</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[0,4,6];9:[4,6];7:[4,6];1:[4];3:[1];4:[0,4,6];2:[4,6];0:[4,6];6:[1,4];8:[4,6]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=36,experts=[0,4,6]; c9:bw=29,experts=[4,6]; c7:bw=26,experts=[4,6]; c1:bw=17,experts=[4]; c3:bw=17,experts=[1]; c4:bw=32,experts=[0,4,6]; c2:bw=24,experts=[4,6]; c0:bw=26,experts=[4,6]; c6:bw=22,experts=[1,4]; c8:bw=28,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>8.0686,4.5525,5.7619,5.1578,6.0449,8.0448,4.5417,5.6749,8.1533,6.3834</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:09:42</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.44711597894527</v>
+      </c>
+      <c r="F82" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>81</v>
+      </c>
+      <c r="I82" t="n">
+        <v>61.9484</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:01.95</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>60.4291</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.3643</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4123.6091</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:08:43.61</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:29;2:25;3:37;1:27;4:23;5:17;9:15;7:32;8:26;0:28</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[3,4];2:[3,4];3:[3,4,6];1:[0,4];4:[1,4];5:[1];9:[1];7:[0,4,6];8:[1,4];0:[1,4]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[3,4]; c2:bw=25,experts=[3,4]; c3:bw=37,experts=[3,4,6]; c1:bw=27,experts=[0,4]; c4:bw=23,experts=[1,4]; c5:bw=17,experts=[1]; c9:bw=15,experts=[1]; c7:bw=32,experts=[0,4,6]; c8:bw=26,experts=[1,4]; c0:bw=28,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>7.9397,4.4439,6.0580,5.1387,7.9671,7.3973,4.2076,5.4519,6.2668,5.5580</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:10:43</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.443736999605851</v>
+      </c>
+      <c r="F83" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="G83" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H83" t="n">
+        <v>82</v>
+      </c>
+      <c r="I83" t="n">
+        <v>61.1868</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:01.19</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>59.6822</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.3553</v>
+      </c>
+      <c r="N83" t="n">
+        <v>4184.8379</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:09:44.84</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:36;0:17;6:20;8:32;7:22;3:22;2:16;9:31;5:22;4:16</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[3,4,6];0:[3];6:[2,4];8:[3,4,6];7:[3,4];3:[4,5];2:[5];9:[3,4,6];5:[3,4];4:[3]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=36,experts=[3,4,6]; c0:bw=17,experts=[3]; c6:bw=20,experts=[2,4]; c8:bw=32,experts=[3,4,6]; c7:bw=22,experts=[3,4]; c3:bw=22,experts=[4,5]; c2:bw=16,experts=[5]; c9:bw=31,experts=[3,4,6]; c5:bw=22,experts=[3,4]; c4:bw=16,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>5.0648,5.5286,7.8384,6.2355,5.3359,5.9523,4.3729,4.1487,7.3025,7.9027</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:11:45</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.457902165393113</v>
+      </c>
+      <c r="F84" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="G84" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H84" t="n">
+        <v>82</v>
+      </c>
+      <c r="I84" t="n">
+        <v>61.5814</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:01.58</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>59.9964</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.4289</v>
+      </c>
+      <c r="N84" t="n">
+        <v>4246.4599</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:10:46.46</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:29;4:10;2:23;7:21;5:10;0:10;6:29;1:35;8:22;3:24</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[5,7];4:[5];2:[4,7];7:[4,7];5:[7];0:[5];6:[4,7];1:[2,4,6];8:[4,5];3:[4,7]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[5,7]; c4:bw=10,experts=[5]; c2:bw=23,experts=[4,7]; c7:bw=21,experts=[4,7]; c5:bw=10,experts=[7]; c0:bw=10,experts=[5]; c6:bw=29,experts=[4,7]; c1:bw=35,experts=[2,4,6]; c8:bw=22,experts=[4,5]; c3:bw=24,experts=[4,7]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>4.1262,7.9134,4.4322,5.4418,7.4180,5.6041,7.7528,5.0797,6.2584,5.9699</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:12:48</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.465493028841845</v>
+      </c>
+      <c r="F85" t="n">
+        <v>63.03</v>
+      </c>
+      <c r="G85" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H85" t="n">
+        <v>82</v>
+      </c>
+      <c r="I85" t="n">
+        <v>63.4439</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:03.44</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>61.8525</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1553</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.4346</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4309.9481</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:11:49.95</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:37;3:18;1:32;6:10;9:11;2:20;7:26;5:11;4:15;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[4,6,7];3:[4];1:[4,5,6];6:[4];9:[0];2:[2,4];7:[1,4];5:[2];4:[7];0:[2]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=37,experts=[4,6,7]; c3:bw=18,experts=[4]; c1:bw=32,experts=[4,5,6]; c6:bw=10,experts=[4]; c9:bw=11,experts=[0]; c2:bw=20,experts=[2,4]; c7:bw=26,experts=[1,4]; c5:bw=11,experts=[2]; c4:bw=15,experts=[7]; c0:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>6.5476,6.2323,5.3447,8.0701,4.2977,4.4549,5.5142,7.4414,8.0623,5.8874</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:13:51</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.431454642087989</v>
+      </c>
+      <c r="F86" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="G86" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H86" t="n">
+        <v>82</v>
+      </c>
+      <c r="I86" t="n">
+        <v>63.1863</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:03.19</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>61.6396</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.3871</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4373.1777</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:12:53.18</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:21;2:25;8:39;6:23;1:31;4:23;9:32;3:28;5:10;7:10</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[0,7];2:[4,6];8:[0,4,6];6:[0,4];1:[4,6,7];4:[4,6];9:[2,4,6];3:[2,4];5:[4];7:[4]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=21,experts=[0,7]; c2:bw=25,experts=[4,6]; c8:bw=39,experts=[0,4,6]; c6:bw=23,experts=[0,4]; c1:bw=31,experts=[4,6,7]; c4:bw=23,experts=[4,6]; c9:bw=32,experts=[2,4,6]; c3:bw=28,experts=[2,4]; c5:bw=10,experts=[4]; c7:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>5.8826,4.5602,6.5404,7.8405,5.2695,8.1503,4.2026,6.0803,7.5804,5.5327</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:14:55</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.421521815154628</v>
+      </c>
+      <c r="F87" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="G87" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H87" t="n">
+        <v>82</v>
+      </c>
+      <c r="I87" t="n">
+        <v>63.382</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:03.38</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>61.8168</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.4121</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4436.603</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:13:56.60</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:26;8:15;2:13;6:31;0:17;4:10;7:24;3:15;1:40;9:24</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[4,6];8:[4];2:[1];6:[4,5,6];0:[4];4:[4];7:[2,4];3:[4];1:[0,1,4,6];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=26,experts=[4,6]; c8:bw=15,experts=[4]; c2:bw=13,experts=[1]; c6:bw=31,experts=[4,5,6]; c0:bw=17,experts=[4]; c4:bw=10,experts=[4]; c7:bw=24,experts=[2,4]; c3:bw=15,experts=[4]; c1:bw=40,experts=[0,1,4,6]; c9:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>7.7533,6.5809,4.6737,8.0358,5.6665,7.9585,5.5249,6.0750,5.2455,4.3027</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:15:59</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.427439516951649</v>
+      </c>
+      <c r="F88" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="G88" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H88" t="n">
+        <v>82</v>
+      </c>
+      <c r="I88" t="n">
+        <v>63.7706</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:03.77</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>62.2706</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.3504</v>
+      </c>
+      <c r="N88" t="n">
+        <v>4500.4172</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:15:00.42</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:16;2:37;7:12;5:10;6:33;3:38;4:19;9:21;8:26;0:19</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[4];2:[0,4,6];7:[5];5:[5];6:[0,4,6];3:[0,4,6];4:[2];9:[4,6];8:[2,4];0:[4]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=16,experts=[4]; c2:bw=37,experts=[0,4,6]; c7:bw=12,experts=[5]; c5:bw=10,experts=[5]; c6:bw=33,experts=[0,4,6]; c3:bw=38,experts=[0,4,6]; c4:bw=19,experts=[2]; c9:bw=21,experts=[4,6]; c8:bw=26,experts=[2,4]; c0:bw=19,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>5.3557,4.6210,5.6420,7.7223,8.1853,6.4424,8.1574,4.1747,6.3123,5.6575</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:17:01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.417104681332233</v>
+      </c>
+      <c r="F89" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="G89" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H89" t="n">
+        <v>82</v>
+      </c>
+      <c r="I89" t="n">
+        <v>62.7557</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:02.76</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>61.2445</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.3547</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4563.2156</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:16:03.22</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:24;6:15;3:18;7:23;0:34;4:21;9:17;1:16;5:17;2:25</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[1];3:[1];7:[4,6];0:[0,4,6];4:[0,4];9:[4];1:[4];5:[0];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=24,experts=[4,6]; c6:bw=15,experts=[1]; c3:bw=18,experts=[1]; c7:bw=23,experts=[4,6]; c0:bw=34,experts=[0,4,6]; c4:bw=21,experts=[0,4]; c9:bw=17,experts=[4]; c1:bw=16,experts=[4]; c5:bw=17,experts=[0]; c2:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>6.4954,8.0213,6.2054,5.6038,5.6058,7.8815,4.2266,5.2632,7.4870,4.4545</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:18:04</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.421980072172324</v>
+      </c>
+      <c r="F90" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="G90" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H90" t="n">
+        <v>82</v>
+      </c>
+      <c r="I90" t="n">
+        <v>62.1533</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:02.15</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>60.6861</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.3221</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4625.6194</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:17:05.62</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:17;8:40;2:25;9:34;7:12;5:25;0:10;6:18;4:17;1:23</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[3];8:[0,1,4,6];2:[3,4];9:[1,4,6];7:[0];5:[1,4];0:[1];6:[3];4:[1];1:[4,6]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=17,experts=[3]; c8:bw=40,experts=[0,1,4,6]; c2:bw=25,experts=[3,4]; c9:bw=34,experts=[1,4,6]; c7:bw=12,experts=[0]; c5:bw=25,experts=[1,4]; c0:bw=10,experts=[1]; c6:bw=18,experts=[3]; c4:bw=17,experts=[1]; c1:bw=23,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>6.0861,6.4787,4.5417,4.3038,5.4765,7.2775,5.6420,7.8558,8.0452,4.9788</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:19:04</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.41109524221223</v>
+      </c>
+      <c r="F91" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="G91" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H91" t="n">
+        <v>82</v>
+      </c>
+      <c r="I91" t="n">
+        <v>60.0827</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:00.08</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>58.6898</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.2472</v>
+      </c>
+      <c r="N91" t="n">
+        <v>4685.9523</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:18:05.95</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:40;1:17;3:20;9:35;0:35;6:14;2:12;5:15;8:28;4:20</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[0,3,4,6];1:[3];3:[4,5];9:[3,4,6];0:[3,4,6];6:[2];2:[5];5:[3];8:[3,4];4:[3,4]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=40,experts=[0,3,4,6]; c1:bw=17,experts=[3]; c3:bw=20,experts=[4,5]; c9:bw=35,experts=[3,4,6]; c0:bw=35,experts=[3,4,6]; c6:bw=14,experts=[2]; c2:bw=12,experts=[5]; c5:bw=15,experts=[3]; c8:bw=28,experts=[3,4]; c4:bw=20,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>5.1827,4.8851,5.8887,4.2174,5.7214,8.2656,4.3251,7.2799,5.6904,7.2334</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:20:05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.419870557544895</v>
+      </c>
+      <c r="F92" t="n">
+        <v>63.47</v>
+      </c>
+      <c r="G92" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H92" t="n">
+        <v>82</v>
+      </c>
+      <c r="I92" t="n">
+        <v>60.4989</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:00.50</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>58.9937</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.3561</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4746.4912</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:19:06.49</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:28;9:19;5:29;7:29;3:22;4:30;0:12;6:16;2:10;8:13</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[2,4];9:[5];5:[4,7];7:[4,7];3:[4,7];4:[4,5,6];0:[5];6:[7];2:[7];8:[5]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[2,4]; c9:bw=19,experts=[5]; c5:bw=29,experts=[4,7]; c7:bw=29,experts=[4,7]; c3:bw=22,experts=[4,7]; c4:bw=30,experts=[4,5,6]; c0:bw=12,experts=[5]; c6:bw=16,experts=[7]; c2:bw=10,experts=[7]; c8:bw=13,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>4.8768,4.0683,7.5755,5.5459,5.6993,7.7692,5.6166,7.8972,4.1772,5.7675</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:21:04</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.428005763850972</v>
+      </c>
+      <c r="F93" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="G93" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="H93" t="n">
+        <v>82</v>
+      </c>
+      <c r="I93" t="n">
+        <v>59.1483</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0:59.15</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>57.7129</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.2927</v>
+      </c>
+      <c r="N93" t="n">
+        <v>4805.6857</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:20:05.69</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:16;7:19;1:11;0:16;8:11;6:25;9:31;2:14;5:37;4:15</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[4];7:[1];1:[5];0:[2];8:[7];6:[4,6];9:[0,4,7];2:[2];5:[2,4,6];4:[7]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=16,experts=[4]; c7:bw=19,experts=[1]; c1:bw=11,experts=[5]; c0:bw=16,experts=[2]; c8:bw=11,experts=[7]; c6:bw=25,experts=[4,6]; c9:bw=31,experts=[0,4,7]; c2:bw=14,experts=[2]; c5:bw=37,experts=[2,4,6]; c4:bw=15,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>5.8463,5.3788,4.8859,5.1791,5.8721,7.6073,4.2247,4.3632,6.9230,7.4325</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:22:02</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.401592176476997</v>
+      </c>
+      <c r="F94" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="G94" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="H94" t="n">
+        <v>93</v>
+      </c>
+      <c r="I94" t="n">
+        <v>57.8066</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0:57.81</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>56.2787</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.3761</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4863.5314</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:21:03.53</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:26;3:17;7:12;9:32;6:12;8:10;5:10;4:18;0:10;2:28</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[4,7];3:[2];7:[4];9:[2,4,6];6:[4];8:[4];5:[4];4:[4];0:[7];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=26,experts=[4,7]; c3:bw=17,experts=[2]; c7:bw=12,experts=[4]; c9:bw=32,experts=[2,4,6]; c6:bw=12,experts=[4]; c8:bw=10,experts=[4]; c5:bw=10,experts=[4]; c4:bw=18,experts=[4]; c0:bw=10,experts=[7]; c2:bw=28,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>4.7077,5.6063,5.2020,3.8535,7.3550,5.9757,6.8814,7.3540,5.0870,4.2559</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:22:59</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.383393703783547</v>
+      </c>
+      <c r="F95" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="G95" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="H95" t="n">
+        <v>93</v>
+      </c>
+      <c r="I95" t="n">
+        <v>57.6129</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0:57.61</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>56.1493</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.3194</v>
+      </c>
+      <c r="N95" t="n">
+        <v>4921.1897</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:22:01.19</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:25;2:36;5:23;4:17;6:17;9:28;1:39;8:10;0:31;3:19</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[2,4];2:[1,4,6];5:[4,6];4:[4];6:[5];9:[4,6];1:[0,1,4];8:[4];0:[0,4,6];3:[4]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=25,experts=[2,4]; c2:bw=36,experts=[1,4,6]; c5:bw=23,experts=[4,6]; c4:bw=17,experts=[4]; c6:bw=17,experts=[5]; c9:bw=28,experts=[4,6]; c1:bw=39,experts=[0,1,4]; c8:bw=10,experts=[4]; c0:bw=31,experts=[0,4,6]; c3:bw=19,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>5.3388,4.3011,7.2595,7.2433,7.0185,3.7719,4.5462,5.8499,5.1872,5.6329</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:23:56</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.390400556723155</v>
+      </c>
+      <c r="F96" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="G96" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="H96" t="n">
+        <v>93</v>
+      </c>
+      <c r="I96" t="n">
+        <v>56.6003</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0:56.60</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>55.2392</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4977.828</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:22:57.83</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:33;9:23;4:10;6:22;0:19;3:23;1:17;8:40;2:13;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[4,5,6];9:[4,6];4:[2];6:[0,4];0:[4];3:[0,6];1:[4];8:[2,4,5,6];2:[0];5:[5]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=33,experts=[4,5,6]; c9:bw=23,experts=[4,6]; c4:bw=10,experts=[2]; c6:bw=22,experts=[0,4]; c0:bw=19,experts=[4]; c3:bw=23,experts=[0,6]; c1:bw=17,experts=[4]; c8:bw=40,experts=[2,4,5,6]; c2:bw=13,experts=[0]; c5:bw=10,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>5.1027,3.7426,7.3980,7.1141,5.2815,5.5605,4.7229,5.7143,4.0855,6.5171</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:24:54</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.374498151319246</v>
+      </c>
+      <c r="F97" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="G97" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
+      <c r="I97" t="n">
+        <v>58.2268</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0:58.23</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>56.8183</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5036.0957</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:23:56.10</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:36;9:25;3:25;1:20;5:33;4:27;6:17;7:28;0:20;8:36</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,4,6];9:[4,6];3:[1,4];1:[4,6];5:[0,4,6];4:[0,4];6:[1];7:[4,6];0:[4,6];8:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=36,experts=[0,4,6]; c9:bw=25,experts=[4,6]; c3:bw=25,experts=[1,4]; c1:bw=20,experts=[4,6]; c5:bw=33,experts=[0,4,6]; c4:bw=27,experts=[0,4]; c6:bw=17,experts=[1]; c7:bw=28,experts=[4,6]; c0:bw=20,experts=[4,6]; c8:bw=36,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>4.0072,3.8547,5.4230,4.7462,7.2507,7.7282,7.4687,5.0945,5.3766,5.8685</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:25:50</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.369768980292124</v>
+      </c>
+      <c r="F98" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>97</v>
+      </c>
+      <c r="I98" t="n">
+        <v>55.2421</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0:55.24</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.1924</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5091.3751</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:24:51.38</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:23;9:24;8:24;4:10;7:17;1:28;3:19;5:26;6:28;2:30</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[1,4];9:[1,4];8:[1,4];4:[1];7:[4];1:[4,6];3:[3];5:[1,4];6:[3,4];2:[3,4,6]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=23,experts=[1,4]; c9:bw=24,experts=[1,4]; c8:bw=24,experts=[1,4]; c4:bw=10,experts=[1]; c7:bw=17,experts=[4]; c1:bw=28,experts=[4,6]; c3:bw=19,experts=[3]; c5:bw=26,experts=[1,4]; c6:bw=28,experts=[3,4]; c2:bw=30,experts=[3,4,6]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5.1979,3.7755,5.3565,7.1809,5.1360,4.6630,5.4522,6.3173,6.8167,4.0139</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:26:45</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.398437866515852</v>
+      </c>
+      <c r="F99" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="G99" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>97</v>
+      </c>
+      <c r="I99" t="n">
+        <v>55.508</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0:55.51</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>54.1317</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.2359</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5146.9209</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:25:46.92</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:29;8:30;9:15;7:13;6:20;5:27;0:19;3:14;1:15;2:13</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[3,4];8:[3,4,6];9:[3];7:[0];6:[2,4];5:[3,4];0:[3];3:[5];1:[3];2:[5]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=29,experts=[3,4]; c8:bw=30,experts=[3,4,6]; c9:bw=15,experts=[3]; c7:bw=13,experts=[0]; c6:bw=20,experts=[2,4]; c5:bw=27,experts=[3,4]; c0:bw=19,experts=[3]; c3:bw=14,experts=[5]; c1:bw=15,experts=[3]; c2:bw=13,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>6.9080,5.5422,3.6480,4.6345,7.0478,6.8873,5.2419,5.5904,4.7582,3.8733</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:27:41</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.393517937375882</v>
+      </c>
+      <c r="F100" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="G100" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>97</v>
+      </c>
+      <c r="I100" t="n">
+        <v>56.0152</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0:56.02</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>54.6533</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.2276</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5202.9762</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:26:42.98</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:19;5:27;7:25;1:33;3:21;9:11;4:14;0:22;2:17;6:19</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[4];5:[4,7];7:[3,7];1:[2,4,6];3:[4,7];9:[5];4:[5];0:[4,5];2:[7];6:[7]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=19,experts=[4]; c5:bw=27,experts=[4,7]; c7:bw=25,experts=[3,7]; c1:bw=33,experts=[2,4,6]; c3:bw=21,experts=[4,7]; c9:bw=11,experts=[5]; c4:bw=14,experts=[5]; c0:bw=22,experts=[4,5]; c2:bw=17,experts=[7]; c6:bw=19,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>5.4400,6.8904,4.8943,4.6557,5.4338,3.6336,7.0987,5.2751,4.0953,7.2363</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:28:35</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.390086707977886</v>
+      </c>
+      <c r="F101" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="G101" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>97</v>
+      </c>
+      <c r="I101" t="n">
+        <v>53.7863</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0:53.79</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>52.4306</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.2121</v>
+      </c>
+      <c r="N101" t="n">
+        <v>5256.8017</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:27:36.80</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:17;8:25;9:29;5:10;6:25;1:10;4:36;7:10;3:23;0:36</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[2];8:[4,7];9:[0,7];5:[2];6:[4,6];1:[5];4:[4,6,7];7:[1];3:[4,6];0:[2,4,6]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=17,experts=[2]; c8:bw=25,experts=[4,7]; c9:bw=29,experts=[0,7]; c5:bw=10,experts=[2]; c6:bw=25,experts=[4,6]; c1:bw=10,experts=[5]; c4:bw=36,experts=[4,6,7]; c7:bw=10,experts=[1]; c3:bw=23,experts=[4,6]; c0:bw=36,experts=[2,4,6]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>4.0208,5.3864,3.5212,6.4294,6.9188,4.5142,7.1874,4.5822,5.0624,4.8078</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
